--- a/artfynd/A 25398-2026 artfynd.xlsx
+++ b/artfynd/A 25398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137431251</v>
       </c>
       <c r="B2" t="n">
-        <v>87481</v>
+        <v>87482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137429860</v>
       </c>
       <c r="B3" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137433419</v>
       </c>
       <c r="B4" t="n">
-        <v>87490</v>
+        <v>87491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137429837</v>
       </c>
       <c r="B5" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137431690</v>
       </c>
       <c r="B6" t="n">
-        <v>89390</v>
+        <v>89391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137431762</v>
       </c>
       <c r="B7" t="n">
-        <v>89390</v>
+        <v>89391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137430746</v>
       </c>
       <c r="B8" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137430111</v>
       </c>
       <c r="B9" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137430267</v>
       </c>
       <c r="B10" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137430320</v>
       </c>
       <c r="B11" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137430424</v>
       </c>
       <c r="B12" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137432945</v>
       </c>
       <c r="B13" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137430605</v>
       </c>
       <c r="B14" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137431533</v>
       </c>
       <c r="B15" t="n">
-        <v>99408</v>
+        <v>99409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137430285</v>
       </c>
       <c r="B16" t="n">
-        <v>111426</v>
+        <v>111427</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137432604</v>
       </c>
       <c r="B17" t="n">
-        <v>102562</v>
+        <v>102563</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137429845</v>
       </c>
       <c r="B18" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137430330</v>
       </c>
       <c r="B19" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 25398-2026 artfynd.xlsx
+++ b/artfynd/A 25398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137431251</v>
       </c>
       <c r="B2" t="n">
-        <v>87482</v>
+        <v>87485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137429860</v>
       </c>
       <c r="B3" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137433419</v>
       </c>
       <c r="B4" t="n">
-        <v>87491</v>
+        <v>87494</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137429837</v>
       </c>
       <c r="B5" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137431690</v>
       </c>
       <c r="B6" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137431762</v>
       </c>
       <c r="B7" t="n">
-        <v>89391</v>
+        <v>89394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137430746</v>
       </c>
       <c r="B8" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137430111</v>
       </c>
       <c r="B9" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137430267</v>
       </c>
       <c r="B10" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137430320</v>
       </c>
       <c r="B11" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137430424</v>
       </c>
       <c r="B12" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137432945</v>
       </c>
       <c r="B13" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137430605</v>
       </c>
       <c r="B14" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137431533</v>
       </c>
       <c r="B15" t="n">
-        <v>99409</v>
+        <v>99412</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137430285</v>
       </c>
       <c r="B16" t="n">
-        <v>111427</v>
+        <v>111430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137432604</v>
       </c>
       <c r="B17" t="n">
-        <v>102563</v>
+        <v>102566</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137429845</v>
       </c>
       <c r="B18" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137430330</v>
       </c>
       <c r="B19" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 25398-2026 artfynd.xlsx
+++ b/artfynd/A 25398-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137431251</v>
       </c>
       <c r="B2" t="n">
-        <v>87485</v>
+        <v>87489</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137429860</v>
       </c>
       <c r="B3" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137433419</v>
       </c>
       <c r="B4" t="n">
-        <v>87494</v>
+        <v>87498</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137429837</v>
       </c>
       <c r="B5" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137431690</v>
       </c>
       <c r="B6" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137431762</v>
       </c>
       <c r="B7" t="n">
-        <v>89394</v>
+        <v>89398</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137430746</v>
       </c>
       <c r="B8" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137430111</v>
       </c>
       <c r="B9" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137430267</v>
       </c>
       <c r="B10" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137430320</v>
       </c>
       <c r="B11" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137430424</v>
       </c>
       <c r="B12" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137432945</v>
       </c>
       <c r="B13" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137430605</v>
       </c>
       <c r="B14" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137431533</v>
       </c>
       <c r="B15" t="n">
-        <v>99412</v>
+        <v>99416</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>137430285</v>
       </c>
       <c r="B16" t="n">
-        <v>111430</v>
+        <v>111436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2213,7 +2213,7 @@
         <v>137432604</v>
       </c>
       <c r="B17" t="n">
-        <v>102566</v>
+        <v>102570</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         <v>137429845</v>
       </c>
       <c r="B18" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>137430330</v>
       </c>
       <c r="B19" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
